--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260610.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260610.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>158,315</t>
+          <t>159,735</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>27.40%</t>
+          <t>26.79%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>114,700</t>
+          <t>115,730</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.42%</t>
+          <t>10.49%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>18,055</t>
+          <t>18,215</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.33%</t>
+          <t>7.12%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>58,455</t>
+          <t>58,955</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>6.89%</t>
+          <t>6.71%</t>
         </is>
       </c>
     </row>
@@ -699,19 +699,19 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>139,095</t>
+          <t>140,395</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.21%</t>
+          <t>5.38%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>C_USD</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -721,12 +721,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>8,538,019</t>
+          <t>341,643,208</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.77%</t>
+          <t>4.86%</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>68,220</t>
+          <t>68,830</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.22%</t>
+          <t>3.29%</t>
         </is>
       </c>
     </row>
@@ -765,12 +765,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>74,815</t>
+          <t>75,565</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.07%</t>
+          <t>3.20%</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>6,535</t>
+          <t>6,635</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.06%</t>
+          <t>3.10%</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>51,705</t>
+          <t>52,255</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.83%</t>
+          <t>2.94%</t>
         </is>
       </c>
     </row>
@@ -831,56 +831,56 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>22,635</t>
+          <t>22,835</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.51%</t>
+          <t>2.49%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>NET US</t>
+          <t>AEP US</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Cloudflare公司</t>
+          <t>美國電力公司</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>20,973</t>
+          <t>36,450</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.19%</t>
+          <t>2.11%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>AEP US</t>
+          <t>NET US</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>美國電力公司</t>
+          <t>Cloudflare公司</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>36,120</t>
+          <t>21,163</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>2.09%</t>
         </is>
       </c>
     </row>
@@ -897,12 +897,12 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>23,275</t>
+          <t>23,485</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.90%</t>
+          <t>1.91%</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>88,415</t>
+          <t>89,115</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.88%</t>
+          <t>1.83%</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>58,575</t>
+          <t>59,125</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.71%</t>
+          <t>1.78%</t>
         </is>
       </c>
     </row>
@@ -963,100 +963,100 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>30,478</t>
+          <t>30,778</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>1.53%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>XEL US</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>維斯達能源公司</t>
+          <t>Xcel 能源</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>22,390</t>
+          <t>41,800</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.47%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>XEL US</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Xcel 能源</t>
+          <t>維斯達能源公司</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>41,500</t>
+          <t>22,590</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.43%</t>
+          <t>1.41%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>ALAB US</t>
+          <t>EXC US</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Astera實驗室公司</t>
+          <t>愛克斯龍公司</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>9,140</t>
+          <t>68,658</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.38%</t>
+          <t>1.41%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>EXC US</t>
+          <t>ALAB US</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>愛克斯龍公司</t>
+          <t>Astera實驗室公司</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>68,008</t>
+          <t>9,240</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.36%</t>
+          <t>1.38%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>13,461</t>
+          <t>13,561</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>1.29%</t>
         </is>
       </c>
     </row>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>24,508</t>
+          <t>24,728</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>1.20%</t>
         </is>
       </c>
     </row>
@@ -1117,12 +1117,12 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>11,016</t>
+          <t>11,116</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.19%</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>145,195</t>
+          <t>146,895</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>1.11%</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>21,215</t>
+          <t>21,415</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>1.10%</t>
         </is>
       </c>
     </row>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>22,647</t>
+          <t>22,847</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1195,66 +1195,66 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>AEE US</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>阿莫林公司</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>68,587,890</t>
+          <t>18,491</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.91%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>AEE US</t>
+          <t>CNP US</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>阿莫林公司</t>
+          <t>Centerpoint能源</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>18,311</t>
+          <t>43,440</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>0.84%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>CNP US</t>
+          <t>PPL US</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Centerpoint能源</t>
+          <t>PPL Corp</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>43,040</t>
+          <t>50,070</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.80%</t>
         </is>
       </c>
     </row>
@@ -1271,41 +1271,41 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>13,615</t>
+          <t>13,765</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>0.75%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>PPL US</t>
+          <t>C_USD</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>PPL Corp</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>49,520</t>
+          <t>1,390,199</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>0.63%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>RDI_NTD</t>
+          <t>RDI_USD</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -1315,32 +1315,10 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>211,974,600</t>
+          <t>-24,157</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>RDI_USD</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>-470,610</t>
-        </is>
-      </c>
-      <c r="D54" s="4" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
